--- a/quizzes/037_sofa_recommendation_quiz_template--quizzes.xlsx
+++ b/quizzes/037_sofa_recommendation_quiz_template--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_question</t>
+          <t>size</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_question</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the customer's preferred size for the sofa?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select a size</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>material</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>choose_a_size</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What material does the customer prefer for the sofa?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select a material</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +574,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>choose_a_material</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What color does the customer prefer for the sofa?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please select a color</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +601,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>style</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>choose_a_color</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What style does the customer prefer for the sofa?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please select a style</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>style</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>choose_a_style</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What pattern does the customer prefer for the sofa?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please select a pattern</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,64 +655,76 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>comfort</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>choose_a_pattern</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What comfort level is the customer expecting?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please select a comfort level</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>comfort</t>
+          <t>fabric_type_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>choose_a_comfort_level</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What type of fabric does the customer prefer?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please select a fabric type</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>price_range</t>
+          <t>fabric_type_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>choose_a_price_range</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What other type of fabric does the customer prefer?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please select another fabric type</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,35 +736,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fabric_type</t>
+          <t>fabric_type_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>choose_a_fabric_type</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is another type of fabric the customer prefers?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please select another fabric type</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fabric_type_2</t>
+          <t>other_fabrics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>choose_another_fabric_type</t>
+          <t>Are there any other fabrics the customer would like to add?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,113 +781,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fabric_type_3</t>
+          <t>submit_note</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>choose_another_fabric_type</t>
+          <t>A short note about the recommended sofa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fabric_type_4</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>choose_another_fabric_type</t>
+          <t>Additional information for the customer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>fabric_type_5</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>choose_another_fabric_type</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>other_fabrics</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>other_fabrics</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,12 +835,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -896,34 +863,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>size_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>size_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -935,12 +902,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -952,12 +919,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>extra_large</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Extra Large</t>
         </is>
       </c>
     </row>
@@ -969,12 +936,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Leather</t>
         </is>
       </c>
     </row>
@@ -986,352 +953,505 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fabric</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fabric</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>color_choices</t>
+          <t>material_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>faux_leather</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Faux Leather</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>color_choices</t>
+          <t>material_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>velvet</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Velvet</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>style_choices</t>
+          <t>color_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>style_choices</t>
+          <t>color_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pattern_choices</t>
+          <t>color_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pattern_choices</t>
+          <t>color_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>comfort_choices</t>
+          <t>style_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>modern</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Modern</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>comfort_choices</t>
+          <t>style_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>classic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Classic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>price_range_choices</t>
+          <t>style_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rustic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rustic</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>price_range_choices</t>
+          <t>style_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>contemporary</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Contemporary</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fabric_type_choices</t>
+          <t>pattern_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>small_pattern</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Small Pattern</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fabric_type_choices</t>
+          <t>pattern_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>large_pattern</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Large Pattern</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fabric_type_2_choices</t>
+          <t>pattern_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no_pattern</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No Pattern</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fabric_type_2_choices</t>
+          <t>pattern_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>random_pattern</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Random Pattern</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fabric_type_3_choices</t>
+          <t>comfort_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fabric_type_3_choices</t>
+          <t>comfort_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>fabric_type_4_choices</t>
+          <t>comfort_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fabric_type_4_choices</t>
+          <t>fabric_type_1_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>cotton</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Cotton</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fabric_type_5_choices</t>
+          <t>fabric_type_1_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>polyester</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Polyester</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fabric_type_5_choices</t>
+          <t>fabric_type_1_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>linen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Linen</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>fabric_type_1_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>silk</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Silk</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>fabric_type_2_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>microfiber</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Microfiber</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>fabric_type_2_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>faux_fur</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Faux Fur</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fabric_type_2_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>velvet</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Velvet</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>fabric_type_2_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Leather</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fabric_type_3_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>denim</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Denim</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fabric_type_3_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>chenille</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chenille</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>fabric_type_3_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>rayon</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Rayon</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fabric_type_3_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>lace</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Lace</t>
         </is>
       </c>
     </row>
